--- a/DateBase/orders/Nha Thu_2026-5-23.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-23.xlsx
@@ -1586,6 +1586,9 @@
       <c r="G2" t="str">
         <v>01530102015155915810209091010955755.84.572051077325551515205155551551010205510101510152010101010302010510105510106215410105555305101062010551015101510105510510080510534575555551010510151055510105101010</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
